--- a/deliverables/10-06_EN.xlsx
+++ b/deliverables/10-06_EN.xlsx
@@ -131,7 +131,7 @@
     <t xml:space="preserve">Non-dedicated solvent pump line</t>
   </si>
   <si>
-    <t xml:space="preserve">316L activation reactor, 1000 L</t>
+    <t xml:space="preserve">316L activation tank, 1000 L</t>
   </si>
   <si>
     <t xml:space="preserve">TJ4S-1213-Sy12-R01</t>
